--- a/JsonConverter/ExcelFiles/SkillTable.xlsx
+++ b/JsonConverter/ExcelFiles/SkillTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="UnitTable" sheetId="1" r:id="rId4"/>
@@ -19,35 +19,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+  <x:si>
+    <x:t>AssembledMaxTargetCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 범위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Range</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>stirng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브레이브 버스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AreaDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skill_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cooldown</x:t>
+  </x:si>
   <x:si>
     <x:t>재사용 대기시간</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬 범위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cooldown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>stirng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
     <x:t>DisplayName</x:t>
   </x:si>
   <x:si>
@@ -63,25 +84,22 @@
     <x:t>기본 공격력 배율</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
+    <x:t>AssembledDamageMultiplier</x:t>
   </x:si>
   <x:si>
     <x:t>MaxTargetCount</x:t>
   </x:si>
   <x:si>
-    <x:t>Range</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브레이브 버스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AreaDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skill_001</x:t>
+    <x:t>AssembledRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합체 상태 공격력 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합체 상태 최대 대상 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합체 상태 범위</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -129,26 +147,11 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="맑은 고딕"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="맑은 고딕"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff008000"/>
+    </x:font>
   </x:fonts>
   <x:fills count="8">
     <x:fill>
@@ -227,8 +230,8 @@
       <x:left style="thin">
         <x:color rgb="ff000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="ff000000"/>
+      <x:right>
+        <x:color auto="1"/>
       </x:right>
       <x:top style="thin">
         <x:color rgb="ff000000"/>
@@ -292,10 +295,10 @@
     <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -911,90 +914,118 @@
     <x:col min="4" max="4" width="15.85546875" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="13" style="3" customWidth="1"/>
     <x:col min="6" max="6" width="17" style="3" customWidth="1"/>
-    <x:col min="7" max="7" width="15" style="3" customWidth="1"/>
-    <x:col min="8" max="9" width="13" style="3" customWidth="1"/>
-    <x:col min="10" max="10" width="23.4296875" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="27.71484375" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="17" style="3" customWidth="1"/>
+    <x:col min="9" max="9" width="25.4296875" style="3" customWidth="1"/>
+    <x:col min="10" max="10" width="15" style="3" customWidth="1"/>
     <x:col min="11" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="13" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="13" t="s">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C1" s="13" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="13.199999999999999">
+      <x:c r="A2" s="13" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B2" s="13" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="13" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E2" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F2" s="13" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G2" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H2" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I2" s="13" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="13.199999999999999">
-      <x:c r="A2" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B2" s="13" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="13" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="13" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E2" s="13" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F2" s="13" t="s">
+      <x:c r="J3" s="14" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="17" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="17" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="s">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="15" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D4" s="2">
         <x:v>3</x:v>
@@ -1002,15 +1033,21 @@
       <x:c r="E4" s="2">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F4" s="16">
+      <x:c r="F4" s="17">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G4" s="2">
+      <x:c r="G4" s="15">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H4" s="15">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I4" s="15">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
+      <x:c r="J4" s="2">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
       <x:c r="M4" s="5"/>
